--- a/docs/ZipCodes_Areas_CCC.xlsx
+++ b/docs/ZipCodes_Areas_CCC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vickimitchell/Code/ICFWA/GG-Integration/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{56EA95D4-CBEA-994F-9DDC-8F20364EB096}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07F7587A-19F0-2A4B-97DB-1235E7C420E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8260" yWindow="2760" windowWidth="16240" windowHeight="18680" xr2:uid="{2E13E25D-8738-4356-9DAE-4DDAC1CF3B2A}"/>
   </bookViews>
@@ -76,9 +76,6 @@
     <t>Zip</t>
   </si>
   <si>
-    <t>SEATTLE CORE</t>
-  </si>
-  <si>
     <t>SEATTLE</t>
   </si>
   <si>
@@ -230,6 +227,9 @@
   </si>
   <si>
     <t>Region</t>
+  </si>
+  <si>
+    <t>GREATER SOUTH SEATTLE</t>
   </si>
 </sst>
 </file>
@@ -649,7 +649,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -660,10 +660,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C2" s="1">
         <v>98118</v>
@@ -671,10 +671,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3" s="1">
         <v>98144</v>
@@ -682,10 +682,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" s="1">
         <v>98104</v>
@@ -693,10 +693,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" s="1">
         <v>98119</v>
@@ -704,10 +704,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" s="1">
         <v>98126</v>
@@ -715,10 +715,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C7" s="1">
         <v>98122</v>
@@ -726,10 +726,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C8" s="1">
         <v>98112</v>
@@ -737,10 +737,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C9" s="1">
         <v>98136</v>
@@ -748,10 +748,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C10" s="1">
         <v>98121</v>
@@ -759,10 +759,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" s="1">
         <v>98101</v>
@@ -770,10 +770,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C12" s="1">
         <v>98116</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C13" s="1">
         <v>98122</v>
@@ -792,10 +792,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" s="1">
         <v>98102</v>
@@ -803,10 +803,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C15" s="1">
         <v>98109</v>
@@ -814,10 +814,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" s="1">
         <v>98108</v>
@@ -825,10 +825,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C17" s="1">
         <v>98116</v>
@@ -836,10 +836,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C18" s="1">
         <v>98112</v>
@@ -847,10 +847,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C19" s="1">
         <v>98126</v>
@@ -858,10 +858,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C20" s="1">
         <v>98118</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C21" s="1">
         <v>98108</v>
@@ -880,10 +880,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>7</v>
       </c>
       <c r="C22" s="1">
         <v>98008</v>
@@ -891,10 +891,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>7</v>
       </c>
       <c r="C23" s="1">
         <v>98004</v>
@@ -902,10 +902,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>7</v>
       </c>
       <c r="C24" s="1">
         <v>98009</v>
@@ -913,10 +913,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>7</v>
       </c>
       <c r="C25" s="1">
         <v>98006</v>
@@ -924,10 +924,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C26" s="1">
         <v>98039</v>
@@ -935,10 +935,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C27" s="1">
         <v>98065</v>
@@ -946,10 +946,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C28" s="1">
         <v>98027</v>
@@ -957,10 +957,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C29" s="1">
         <v>98045</v>
@@ -968,10 +968,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C30" s="1">
         <v>98057</v>
@@ -979,10 +979,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C31" s="1">
         <v>98074</v>
@@ -990,10 +990,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C32" s="1">
         <v>98075</v>
@@ -1001,10 +1001,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C33" s="1">
         <v>98029</v>
@@ -1012,10 +1012,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>7</v>
       </c>
       <c r="C34" s="1">
         <v>98007</v>
@@ -1023,10 +1023,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>7</v>
       </c>
       <c r="C35" s="1">
         <v>98005</v>
@@ -1034,10 +1034,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C36" s="1">
         <v>98059</v>
@@ -1045,10 +1045,10 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C37" s="1">
         <v>98024</v>
@@ -1056,10 +1056,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C38" s="1">
         <v>98056</v>
@@ -1067,10 +1067,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C39" s="1">
         <v>98006</v>
@@ -1078,10 +1078,10 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C40" s="1">
         <v>98007</v>
@@ -1089,10 +1089,10 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="C41" s="1">
         <v>98020</v>
@@ -1100,10 +1100,10 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C42" s="1">
         <v>98258</v>
@@ -1111,10 +1111,10 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C43" s="1">
         <v>98011</v>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C44" s="1">
         <v>98275</v>
@@ -1133,10 +1133,10 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C45" s="1">
         <v>98290</v>
@@ -1144,10 +1144,10 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C46" s="1">
         <v>98201</v>
@@ -1155,10 +1155,10 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C47" s="1">
         <v>98021</v>
@@ -1166,10 +1166,10 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C48" s="1">
         <v>98036</v>
@@ -1177,10 +1177,10 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C49" s="1">
         <v>98155</v>
@@ -1188,10 +1188,10 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C50" s="1">
         <v>98208</v>
@@ -1199,10 +1199,10 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C51" s="1">
         <v>98204</v>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C52" s="1">
         <v>98296</v>
@@ -1221,10 +1221,10 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C53" s="1">
         <v>98012</v>
@@ -1232,10 +1232,10 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C54" s="1">
         <v>97215</v>
@@ -1243,10 +1243,10 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C55" s="1">
         <v>98043</v>
@@ -1254,10 +1254,10 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C56" s="1">
         <v>98012</v>
@@ -1265,10 +1265,10 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C57" s="1">
         <v>98037</v>
@@ -1276,10 +1276,10 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C58" s="1">
         <v>98028</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B59" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="C59" s="1">
         <v>98026</v>
@@ -1298,10 +1298,10 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C60" s="1">
         <v>98203</v>
@@ -1309,10 +1309,10 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C61" s="1">
         <v>98082</v>
@@ -1320,10 +1320,10 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C62" s="1">
         <v>98290</v>
@@ -1331,10 +1331,10 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C63" s="1">
         <v>98036</v>
@@ -1342,10 +1342,10 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C64" s="1">
         <v>98258</v>
@@ -1353,10 +1353,10 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C65" s="1">
         <v>98115</v>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C66" s="1">
         <v>98107</v>
@@ -1375,10 +1375,10 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C67" s="1">
         <v>98177</v>
@@ -1386,10 +1386,10 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C68" s="1">
         <v>98125</v>
@@ -1397,10 +1397,10 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C69" s="1">
         <v>98103</v>
@@ -1408,10 +1408,10 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B70" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>33</v>
       </c>
       <c r="C70" s="1">
         <v>98177</v>
@@ -1419,10 +1419,10 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C71" s="1">
         <v>98133</v>
@@ -1430,10 +1430,10 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C72" s="1">
         <v>98117</v>
@@ -1441,10 +1441,10 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C73" s="1">
         <v>98115</v>
@@ -1452,10 +1452,10 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B74" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>33</v>
       </c>
       <c r="C74" s="1">
         <v>98133</v>
@@ -1463,10 +1463,10 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B75" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="C75" s="1">
         <v>98019</v>
@@ -1474,10 +1474,10 @@
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C76" s="1">
         <v>98077</v>
@@ -1485,10 +1485,10 @@
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C77" s="1">
         <v>98033</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C78" s="1">
         <v>98034</v>
@@ -1507,10 +1507,10 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C79" s="1">
         <v>98011</v>
@@ -1518,10 +1518,10 @@
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C80" s="1">
         <v>98033</v>
@@ -1529,10 +1529,10 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C81" s="1">
         <v>98052</v>
@@ -1540,10 +1540,10 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C82" s="1">
         <v>98053</v>
@@ -1551,10 +1551,10 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C83" s="1">
         <v>98021</v>
@@ -1562,10 +1562,10 @@
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C84" s="1">
         <v>98083</v>
@@ -1573,10 +1573,10 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C85" s="1">
         <v>98012</v>
@@ -1584,10 +1584,10 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C86" s="1">
         <v>98072</v>
@@ -1595,10 +1595,10 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C87" s="1">
         <v>98272</v>
@@ -1606,10 +1606,10 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C88" s="1">
         <v>98405</v>
@@ -1617,10 +1617,10 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C89" s="1">
         <v>98408</v>
@@ -1628,10 +1628,10 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>42</v>
       </c>
       <c r="C90" s="1">
         <v>98467</v>
@@ -1639,10 +1639,10 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C91" s="1">
         <v>98023</v>
@@ -1650,10 +1650,10 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C92" s="1">
         <v>98402</v>
@@ -1661,10 +1661,10 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C93" s="1">
         <v>98407</v>
@@ -1672,10 +1672,10 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C94" s="1">
         <v>98404</v>
@@ -1683,10 +1683,10 @@
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C95" s="1">
         <v>98502</v>
@@ -1694,10 +1694,10 @@
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C96" s="1">
         <v>98003</v>
@@ -1705,10 +1705,10 @@
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C97" s="1">
         <v>98516</v>
@@ -1716,10 +1716,10 @@
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C98" s="1">
         <v>98374</v>
@@ -1727,10 +1727,10 @@
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C99" s="1">
         <v>98513</v>
@@ -1738,10 +1738,10 @@
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C100" s="1">
         <v>98446</v>
@@ -1749,10 +1749,10 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C101" s="1">
         <v>98501</v>
@@ -1760,10 +1760,10 @@
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C102" s="1">
         <v>98506</v>
@@ -1771,10 +1771,10 @@
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C103" s="1">
         <v>98512</v>
@@ -1782,10 +1782,10 @@
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C104" s="1">
         <v>98422</v>
@@ -1793,10 +1793,10 @@
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C105" s="1">
         <v>98403</v>
@@ -1804,10 +1804,10 @@
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C106" s="1">
         <v>98422</v>
@@ -1815,10 +1815,10 @@
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C107" s="1">
         <v>98443</v>
@@ -1826,10 +1826,10 @@
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C108" s="1">
         <v>98465</v>
@@ -1837,10 +1837,10 @@
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C109" s="1">
         <v>98516</v>
@@ -1848,10 +1848,10 @@
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C110" s="1">
         <v>98001</v>
@@ -1859,10 +1859,10 @@
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C111" s="1">
         <v>98388</v>
@@ -1870,10 +1870,10 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C112" s="1">
         <v>98375</v>
@@ -1881,10 +1881,10 @@
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C113" s="1">
         <v>98498</v>
@@ -1892,10 +1892,10 @@
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C114" s="1">
         <v>98406</v>
@@ -1903,10 +1903,10 @@
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C115" s="1">
         <v>98387</v>
@@ -1914,10 +1914,10 @@
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B116" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="B116" s="1" t="s">
-        <v>42</v>
       </c>
       <c r="C116" s="1">
         <v>98466</v>
@@ -1925,10 +1925,10 @@
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C117" s="1">
         <v>98371</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C118" s="1">
         <v>98467</v>
